--- a/Example/Excel/Depth.Data.xlsx
+++ b/Example/Excel/Depth.Data.xlsx
@@ -5,23 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubProjects\ExcelToProtobuf_csharp\Example\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\SourceCode\Tools\ExcelToProtobuf_csharp\Example\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF23B2D-F743-4B9E-91E8-88A6AA07E557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB1415D-5B1F-4C5C-B585-F005B58DCAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfoTest" sheetId="2" r:id="rId1"/>
     <sheet name="EnemyInfo" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
   <si>
     <t>编号</t>
   </si>
@@ -69,6 +74,18 @@
   </si>
   <si>
     <t>敌人4</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试敌人1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -281,6 +298,182 @@
     <dxf>
       <border outline="0">
         <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
           <color rgb="FF96AAD8"/>
         </left>
         <right style="thin">
@@ -311,182 +504,6 @@
         <family val="2"/>
         <charset val="134"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -528,26 +545,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:D7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A1:D7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -830,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
@@ -931,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -959,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>

--- a/Example/Excel/Depth.Data.xlsx
+++ b/Example/Excel/Depth.Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\SourceCode\Tools\ExcelToProtobuf_csharp\Example\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB1415D-5B1F-4C5C-B585-F005B58DCAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0389357-039F-4541-B37B-8B97542F1511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
   <si>
     <t>编号</t>
   </si>
@@ -85,6 +85,37 @@
   </si>
   <si>
     <t>测试敌人1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐标1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vector2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pos1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐标2</t>
+  </si>
+  <si>
+    <t>vector3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pos2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4;5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -161,7 +192,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -174,11 +205,75 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -545,26 +640,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A1:D7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:D7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:F7" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A1:F7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{A5A625DA-7AD4-4F95-8501-2208AC55EF3A}" name="坐标1" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F5C83561-0D43-431E-BE1E-27A4E307FD94}" name="坐标2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -923,13 +1020,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="65.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -942,8 +1039,14 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -956,8 +1059,14 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -970,8 +1079,14 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -984,8 +1099,14 @@
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -998,8 +1119,14 @@
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1012,8 +1139,14 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1025,6 +1158,12 @@
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Example/Excel/Depth.Data.xlsx
+++ b/Example/Excel/Depth.Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\SourceCode\Tools\ExcelToProtobuf_csharp\Example\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0389357-039F-4541-B37B-8B97542F1511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9885D80-BC89-42AF-BAA7-C49D8E2AB0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyInfoTest" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
   <si>
     <t>编号</t>
   </si>
@@ -116,6 +116,30 @@
   </si>
   <si>
     <t>4;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试本地化1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试本地化2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试本地化3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试本地化4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -123,7 +147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -147,6 +171,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,7 +223,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -211,11 +242,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -640,28 +703,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:D7" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
-  <autoFilter ref="A1:D7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{887C5756-674A-4C39-96C8-83B92494B4B4}" name="表2_2" displayName="表2_2" ref="A1:E7" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+  <autoFilter ref="A1:E7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A0EEB951-CD5D-4393-B7BF-89A93EDA50E4}" name="编号" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{AF2264B0-5F09-4EC6-A104-754BFE5698D0}" name="名字" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{7A0FCD85-0127-49B1-BBB4-141CF0B0428C}" name="根路径" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{38F009CE-2CF9-4A50-83CC-157FB08B2F7F}" name="路径" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{74BF12CB-254F-4DA0-ACA5-BC71DF6303BD}" name="描述" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:F7" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}" name="表2" displayName="表2" ref="A1:F7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A1:F7" xr:uid="{E6DBE18B-BF56-4735-8F8B-320E00135FE6}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{A5A625DA-7AD4-4F95-8501-2208AC55EF3A}" name="坐标1" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{F5C83561-0D43-431E-BE1E-27A4E307FD94}" name="坐标2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{0B5E45A7-5C33-4A2E-8609-F91796C7CDE2}" name="编号" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7EC0CB57-F7D0-434A-B28A-7BC7CEA24A18}" name="名字" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B2C3DFF9-A8F3-4301-893B-4F499A061463}" name="根路径" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{7DD8349E-9C83-486C-9021-1DD09A9679B2}" name="路径" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{A5A625DA-7AD4-4F95-8501-2208AC55EF3A}" name="坐标1" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{F5C83561-0D43-431E-BE1E-27A4E307FD94}" name="坐标2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -905,13 +969,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C83AA5-F696-4A83-B61F-997B453AB306}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="65.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -924,8 +988,11 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -938,8 +1005,11 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -952,8 +1022,11 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -966,8 +1039,11 @@
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E4" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -980,8 +1056,11 @@
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -994,8 +1073,11 @@
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1007,6 +1089,9 @@
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
